--- a/data/trans_orig/IP33A-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP33A-Clase-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2507</t>
+          <t>2457</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8976</t>
+          <t>8888</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>51,25%</t>
+          <t>50,75%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2637</t>
+          <t>2551</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8112</t>
+          <t>8029</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>21,16%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>67,29%</t>
+          <t>66,6%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6640</t>
+          <t>6810</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>14993</t>
+          <t>15547</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>50,7%</t>
+          <t>52,58%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8538</t>
+          <t>8626</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15007</t>
+          <t>15057</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>48,75%</t>
+          <t>49,25%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>85,69%</t>
+          <t>85,97%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>3943</t>
+          <t>4026</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9418</t>
+          <t>9504</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>32,71%</t>
+          <t>33,4%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>78,12%</t>
+          <t>78,84%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>14576</t>
+          <t>14022</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>22929</t>
+          <t>22759</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>49,3%</t>
+          <t>47,42%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>77,54%</t>
+          <t>76,97%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1817</t>
+          <t>1348</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7013</t>
+          <t>6751</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>61,35%</t>
+          <t>59,06%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4437</t>
+          <t>4448</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9755</t>
+          <t>9724</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>38,32%</t>
+          <t>38,42%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>84,25%</t>
+          <t>83,99%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7150</t>
+          <t>7464</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>15136</t>
+          <t>14967</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>31,07%</t>
+          <t>32,44%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>65,78%</t>
+          <t>65,05%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>4419</t>
+          <t>4681</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>9615</t>
+          <t>10084</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>38,65%</t>
+          <t>40,94%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>84,1%</t>
+          <t>88,21%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1823</t>
+          <t>1854</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>7141</t>
+          <t>7130</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>61,68%</t>
+          <t>61,58%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>7874</t>
+          <t>8043</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>15860</t>
+          <t>15546</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>34,22%</t>
+          <t>34,95%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>68,93%</t>
+          <t>67,56%</t>
         </is>
       </c>
     </row>
@@ -1419,7 +1419,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>538</t>
+          <t>505</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -1434,7 +1434,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3863</t>
+          <t>3512</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>42,18%</t>
+          <t>38,35%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1234</t>
+          <t>1204</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6226</t>
+          <t>6702</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>48,42%</t>
+          <t>52,12%</t>
         </is>
       </c>
     </row>
@@ -1537,7 +1537,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3161</t>
+          <t>3194</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>85,47%</t>
+          <t>86,36%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5296</t>
+          <t>5647</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>57,82%</t>
+          <t>61,65%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>6632</t>
+          <t>6156</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>11624</t>
+          <t>11654</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>51,58%</t>
+          <t>47,88%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>90,4%</t>
+          <t>90,63%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4676</t>
+          <t>4652</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12178</t>
+          <t>12206</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,18%</t>
+          <t>16,1%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>42,14%</t>
+          <t>42,24%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>8257</t>
+          <t>7880</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17226</t>
+          <t>17132</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>22,3%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>48,75%</t>
+          <t>48,48%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>14720</t>
+          <t>14706</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>26463</t>
+          <t>26310</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>22,89%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>41,2%</t>
+          <t>40,96%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>16719</t>
+          <t>16691</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>24221</t>
+          <t>24245</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>57,86%</t>
+          <t>57,76%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,82%</t>
+          <t>83,9%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>18113</t>
+          <t>18207</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>27082</t>
+          <t>27459</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>51,25%</t>
+          <t>51,52%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>76,63%</t>
+          <t>77,7%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>37774</t>
+          <t>37927</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>49517</t>
+          <t>49531</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>58,8%</t>
+          <t>59,04%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>77,09%</t>
+          <t>77,11%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4327</t>
+          <t>4457</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11642</t>
+          <t>11180</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>20,08%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>52,44%</t>
+          <t>50,36%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5593</t>
+          <t>5756</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13194</t>
+          <t>12816</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>28,98%</t>
+          <t>29,83%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>68,36%</t>
+          <t>66,41%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>11237</t>
+          <t>12082</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>22288</t>
+          <t>22525</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>27,08%</t>
+          <t>29,11%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>53,71%</t>
+          <t>54,28%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10559</t>
+          <t>11021</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>17874</t>
+          <t>17744</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>47,56%</t>
+          <t>49,64%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>80,51%</t>
+          <t>79,92%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>6105</t>
+          <t>6483</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>13706</t>
+          <t>13543</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>31,64%</t>
+          <t>33,59%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>71,02%</t>
+          <t>70,17%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>19211</t>
+          <t>18974</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>30262</t>
+          <t>29417</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>46,29%</t>
+          <t>45,72%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>72,92%</t>
+          <t>70,89%</t>
         </is>
       </c>
     </row>
@@ -2453,7 +2453,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4500</t>
+          <t>3849</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2468,7 +2468,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>49,35%</t>
+          <t>42,21%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>831</t>
+          <t>686</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5922</t>
+          <t>5667</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>57,74%</t>
+          <t>55,25%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1548</t>
+          <t>1567</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>8088</t>
+          <t>7804</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>41,75%</t>
+          <t>40,28%</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4618</t>
+          <t>5269</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>50,65%</t>
+          <t>57,79%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>4334</t>
+          <t>4589</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>9425</t>
+          <t>9570</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>42,26%</t>
+          <t>44,75%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>91,9%</t>
+          <t>93,31%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>11286</t>
+          <t>11570</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>17826</t>
+          <t>17807</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>58,25%</t>
+          <t>59,72%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>92,01%</t>
+          <t>91,91%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>22145</t>
+          <t>21112</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>36712</t>
+          <t>36087</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>22,73%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>39,53%</t>
+          <t>38,86%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>30746</t>
+          <t>30585</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>46732</t>
+          <t>46309</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>31,47%</t>
+          <t>31,31%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>47,84%</t>
+          <t>47,41%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>56255</t>
+          <t>56300</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>77284</t>
+          <t>78423</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>29,52%</t>
+          <t>29,55%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>40,56%</t>
+          <t>41,16%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>56149</t>
+          <t>56774</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>70716</t>
+          <t>71749</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>60,47%</t>
+          <t>61,14%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>76,15%</t>
+          <t>77,27%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>50954</t>
+          <t>51377</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>66940</t>
+          <t>67101</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>52,16%</t>
+          <t>52,59%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>68,53%</t>
+          <t>68,69%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>113263</t>
+          <t>112124</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>134292</t>
+          <t>134247</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>59,44%</t>
+          <t>58,84%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>70,48%</t>
+          <t>70,45%</t>
         </is>
       </c>
     </row>
@@ -3368,12 +3368,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>4626</t>
+          <t>4650</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10201</t>
+          <t>10154</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>37,76%</t>
+          <t>37,97%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>83,28%</t>
+          <t>82,9%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3403,12 +3403,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2953</t>
+          <t>2848</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8445</t>
+          <t>8129</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>26,75%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>79,31%</t>
+          <t>76,34%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9500</t>
+          <t>9992</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>17213</t>
+          <t>17373</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3453,12 +3453,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>41,49%</t>
+          <t>43,64%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>75,17%</t>
+          <t>75,88%</t>
         </is>
       </c>
     </row>
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2048</t>
+          <t>2095</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7623</t>
+          <t>7599</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3496,12 +3496,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>62,24%</t>
+          <t>62,03%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2203</t>
+          <t>2519</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7695</t>
+          <t>7800</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>23,66%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>72,27%</t>
+          <t>73,25%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>5684</t>
+          <t>5524</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>13397</t>
+          <t>12905</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3566,12 +3566,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>24,12%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>58,51%</t>
+          <t>56,36%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1202</t>
+          <t>1249</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6273</t>
+          <t>6530</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>48,36%</t>
+          <t>50,34%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1960</t>
+          <t>1897</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>7372</t>
+          <t>7640</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>12,97%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>50,4%</t>
+          <t>52,23%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4419</t>
+          <t>4404</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>11953</t>
+          <t>11784</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>15,96%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>43,31%</t>
+          <t>42,7%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>6698</t>
+          <t>6441</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>11769</t>
+          <t>11722</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>51,64%</t>
+          <t>49,66%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90,73%</t>
+          <t>90,37%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>7255</t>
+          <t>6987</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>12667</t>
+          <t>12730</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>49,6%</t>
+          <t>47,77%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>86,6%</t>
+          <t>87,03%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>15645</t>
+          <t>15814</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>23179</t>
+          <t>23194</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>56,69%</t>
+          <t>57,3%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>83,99%</t>
+          <t>84,04%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>4879</t>
+          <t>5072</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10593</t>
+          <t>10659</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>36,42%</t>
+          <t>37,86%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>79,07%</t>
+          <t>79,56%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2374</t>
+          <t>2607</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8140</t>
+          <t>8159</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,58%</t>
+          <t>23,7%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>74,0%</t>
+          <t>74,17%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9263</t>
+          <t>8931</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>17251</t>
+          <t>16818</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>37,97%</t>
+          <t>36,61%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>70,71%</t>
+          <t>68,94%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2804</t>
+          <t>2738</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8518</t>
+          <t>8325</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>20,44%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>63,58%</t>
+          <t>62,14%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2860</t>
+          <t>2841</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8626</t>
+          <t>8393</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>26,0%</t>
+          <t>25,83%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>78,42%</t>
+          <t>76,3%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>7145</t>
+          <t>7578</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>15133</t>
+          <t>15465</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>29,29%</t>
+          <t>31,06%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>62,03%</t>
+          <t>63,39%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18872</t>
+          <t>19099</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>30207</t>
+          <t>30371</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>38,55%</t>
+          <t>39,01%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>61,7%</t>
+          <t>62,03%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>14845</t>
+          <t>14401</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>26786</t>
+          <t>26442</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>28,93%</t>
+          <t>28,06%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>52,19%</t>
+          <t>51,52%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>36527</t>
+          <t>36101</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>53250</t>
+          <t>52676</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>36,42%</t>
+          <t>36,0%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>53,1%</t>
+          <t>52,53%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>18754</t>
+          <t>18590</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>30089</t>
+          <t>29862</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>38,3%</t>
+          <t>37,97%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>61,45%</t>
+          <t>60,99%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>24536</t>
+          <t>24880</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>36477</t>
+          <t>36921</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>47,81%</t>
+          <t>48,48%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>71,07%</t>
+          <t>71,94%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>47033</t>
+          <t>47607</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>63756</t>
+          <t>64182</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>46,9%</t>
+          <t>47,47%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>63,58%</t>
+          <t>64,0%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8369</t>
+          <t>8790</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>18527</t>
+          <t>18846</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>22,75%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>47,95%</t>
+          <t>48,78%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2007</t>
+          <t>2184</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>8893</t>
+          <t>9196</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>31,48%</t>
+          <t>32,55%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>12314</t>
+          <t>12835</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>25108</t>
+          <t>26011</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>19,19%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>37,54%</t>
+          <t>38,89%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>20110</t>
+          <t>19791</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>30268</t>
+          <t>29847</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>52,05%</t>
+          <t>51,22%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>78,34%</t>
+          <t>77,25%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>19355</t>
+          <t>19052</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>26241</t>
+          <t>26064</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>68,52%</t>
+          <t>67,45%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>92,89%</t>
+          <t>92,27%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>41778</t>
+          <t>40875</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>54572</t>
+          <t>54051</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>62,46%</t>
+          <t>61,11%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>81,59%</t>
+          <t>80,81%</t>
         </is>
       </c>
     </row>
@@ -5088,7 +5088,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4096</t>
+          <t>4084</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>56,02%</t>
+          <t>55,86%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1239</t>
+          <t>1194</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6465</t>
+          <t>6600</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>44,15%</t>
+          <t>45,08%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>1997</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>8882</t>
+          <t>8584</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,23%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>40,46%</t>
+          <t>39,1%</t>
         </is>
       </c>
     </row>
@@ -5196,7 +5196,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3216</t>
+          <t>3228</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>43,98%</t>
+          <t>44,14%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>8177</t>
+          <t>8042</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>13403</t>
+          <t>13448</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>55,85%</t>
+          <t>54,92%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>91,54%</t>
+          <t>91,85%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>13072</t>
+          <t>13370</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>19928</t>
+          <t>19957</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>59,54%</t>
+          <t>60,9%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>90,77%</t>
+          <t>90,9%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>49267</t>
+          <t>48721</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>68767</t>
+          <t>67783</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>36,9%</t>
+          <t>36,49%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>51,5%</t>
+          <t>50,76%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>35658</t>
+          <t>35344</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>53299</t>
+          <t>52684</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>27,33%</t>
+          <t>27,09%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>40,85%</t>
+          <t>40,37%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>88587</t>
+          <t>89978</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>115300</t>
+          <t>117316</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>33,55%</t>
+          <t>34,08%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>43,67%</t>
+          <t>44,44%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>64760</t>
+          <t>65744</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>84260</t>
+          <t>84806</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>48,5%</t>
+          <t>49,24%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>63,1%</t>
+          <t>63,51%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>77189</t>
+          <t>77804</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>94830</t>
+          <t>95144</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>59,15%</t>
+          <t>59,63%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>72,67%</t>
+          <t>72,91%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>148715</t>
+          <t>146699</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>175428</t>
+          <t>174037</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>56,33%</t>
+          <t>55,56%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>66,45%</t>
+          <t>65,92%</t>
         </is>
       </c>
     </row>
@@ -6003,12 +6003,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3609</t>
+          <t>3883</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10621</t>
+          <t>10445</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>55,75%</t>
+          <t>54,83%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6038,12 +6038,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3832</t>
+          <t>3877</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>10752</t>
+          <t>10537</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>21,45%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>59,47%</t>
+          <t>58,28%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6073,12 +6073,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9033</t>
+          <t>9892</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>18812</t>
+          <t>19397</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>24,33%</t>
+          <t>26,64%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>50,67%</t>
+          <t>52,24%</t>
         </is>
       </c>
     </row>
@@ -6116,12 +6116,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8429</t>
+          <t>8605</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>15441</t>
+          <t>15167</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6131,12 +6131,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>44,25%</t>
+          <t>45,17%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>81,06%</t>
+          <t>79,62%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6151,12 +6151,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>7327</t>
+          <t>7542</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>14247</t>
+          <t>14202</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6166,12 +6166,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>40,53%</t>
+          <t>41,72%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>78,8%</t>
+          <t>78,55%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6186,12 +6186,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>18317</t>
+          <t>17732</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>28096</t>
+          <t>27237</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>49,33%</t>
+          <t>47,76%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>75,67%</t>
+          <t>73,36%</t>
         </is>
       </c>
     </row>
@@ -6346,12 +6346,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5638</t>
+          <t>5982</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14364</t>
+          <t>14235</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,2%</t>
+          <t>20,37%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>48,91%</t>
+          <t>48,47%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6381,12 +6381,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4744</t>
+          <t>4673</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12603</t>
+          <t>12104</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20,81%</t>
+          <t>20,5%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>55,28%</t>
+          <t>53,09%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6416,12 +6416,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>12531</t>
+          <t>12212</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>24294</t>
+          <t>24041</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -6431,12 +6431,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>24,02%</t>
+          <t>23,41%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>46,57%</t>
+          <t>46,09%</t>
         </is>
       </c>
     </row>
@@ -6459,12 +6459,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>15004</t>
+          <t>15133</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>23730</t>
+          <t>23386</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>51,09%</t>
+          <t>51,53%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>80,8%</t>
+          <t>79,63%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6494,12 +6494,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>10195</t>
+          <t>10694</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>18054</t>
+          <t>18125</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>44,72%</t>
+          <t>46,91%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>79,19%</t>
+          <t>79,5%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6529,12 +6529,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>27872</t>
+          <t>28125</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>39635</t>
+          <t>39954</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>53,43%</t>
+          <t>53,91%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>75,98%</t>
+          <t>76,59%</t>
         </is>
       </c>
     </row>
@@ -6689,12 +6689,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2884</t>
+          <t>2873</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7849</t>
+          <t>7809</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>27,85%</t>
+          <t>27,74%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>75,79%</t>
+          <t>75,41%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6724,12 +6724,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2959</t>
+          <t>2574</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8336</t>
+          <t>7791</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>26,55%</t>
+          <t>23,1%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>74,8%</t>
+          <t>69,91%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6759,12 +6759,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7138</t>
+          <t>6628</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>14514</t>
+          <t>14673</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6774,12 +6774,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>33,2%</t>
+          <t>30,83%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>67,51%</t>
+          <t>68,25%</t>
         </is>
       </c>
     </row>
@@ -6802,12 +6802,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2507</t>
+          <t>2547</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7472</t>
+          <t>7483</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>24,59%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>72,15%</t>
+          <t>72,26%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6837,12 +6837,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2808</t>
+          <t>3353</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8185</t>
+          <t>8570</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>25,2%</t>
+          <t>30,09%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>73,45%</t>
+          <t>76,9%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6872,12 +6872,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>6986</t>
+          <t>6827</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>14362</t>
+          <t>14872</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6887,12 +6887,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>32,49%</t>
+          <t>31,75%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>66,8%</t>
+          <t>69,17%</t>
         </is>
       </c>
     </row>
@@ -7032,12 +7032,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>22196</t>
+          <t>22678</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>35611</t>
+          <t>35726</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7047,12 +7047,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>31,78%</t>
+          <t>32,47%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>50,99%</t>
+          <t>51,15%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>21366</t>
+          <t>21416</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>34384</t>
+          <t>35137</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7082,12 +7082,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>33,48%</t>
+          <t>33,56%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>53,89%</t>
+          <t>55,06%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7102,12 +7102,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>46911</t>
+          <t>47775</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>66421</t>
+          <t>66361</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>35,1%</t>
+          <t>35,75%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>49,7%</t>
+          <t>49,65%</t>
         </is>
       </c>
     </row>
@@ -7145,12 +7145,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>34227</t>
+          <t>34112</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>47642</t>
+          <t>47160</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>49,01%</t>
+          <t>48,85%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>68,22%</t>
+          <t>67,53%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7180,12 +7180,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>29426</t>
+          <t>28673</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>42444</t>
+          <t>42394</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>46,11%</t>
+          <t>44,94%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>66,52%</t>
+          <t>66,44%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7215,12 +7215,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>67227</t>
+          <t>67287</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>86737</t>
+          <t>85873</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>50,3%</t>
+          <t>50,35%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>64,9%</t>
+          <t>64,25%</t>
         </is>
       </c>
     </row>
@@ -7375,12 +7375,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>11662</t>
+          <t>11491</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>21008</t>
+          <t>20996</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7390,12 +7390,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>29,54%</t>
+          <t>29,1%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>53,21%</t>
+          <t>53,18%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7410,12 +7410,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>11605</t>
+          <t>11178</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>22037</t>
+          <t>21948</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7425,12 +7425,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>26,96%</t>
+          <t>25,97%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>51,19%</t>
+          <t>50,99%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7445,12 +7445,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>25223</t>
+          <t>26050</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>40152</t>
+          <t>39577</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7460,12 +7460,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>30,56%</t>
+          <t>31,56%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>48,65%</t>
+          <t>47,96%</t>
         </is>
       </c>
     </row>
@@ -7488,12 +7488,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>18475</t>
+          <t>18487</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>27821</t>
+          <t>27992</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7503,12 +7503,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>46,79%</t>
+          <t>46,82%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>70,46%</t>
+          <t>70,9%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7523,12 +7523,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>21009</t>
+          <t>21098</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>31441</t>
+          <t>31868</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7538,12 +7538,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>48,81%</t>
+          <t>49,01%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>73,04%</t>
+          <t>74,03%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7558,12 +7558,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>42377</t>
+          <t>42952</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>57306</t>
+          <t>56479</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7573,12 +7573,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>51,35%</t>
+          <t>52,04%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>69,44%</t>
+          <t>68,44%</t>
         </is>
       </c>
     </row>
@@ -7718,12 +7718,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>4878</t>
+          <t>4754</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>11343</t>
+          <t>11383</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -7733,12 +7733,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>27,06%</t>
+          <t>26,37%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>62,92%</t>
+          <t>63,14%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2136</t>
+          <t>2137</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8879</t>
+          <t>9056</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -7773,7 +7773,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>33,91%</t>
+          <t>34,59%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -7788,12 +7788,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>8704</t>
+          <t>8584</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>17960</t>
+          <t>18307</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -7803,12 +7803,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>19,69%</t>
+          <t>19,42%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>40,62%</t>
+          <t>41,41%</t>
         </is>
       </c>
     </row>
@@ -7831,12 +7831,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>6684</t>
+          <t>6644</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>13149</t>
+          <t>13273</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7846,12 +7846,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>37,08%</t>
+          <t>36,86%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>72,94%</t>
+          <t>73,63%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>17304</t>
+          <t>17127</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>24047</t>
+          <t>24046</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7881,7 +7881,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>66,09%</t>
+          <t>65,41%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -7901,12 +7901,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>26250</t>
+          <t>25903</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>35506</t>
+          <t>35626</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7916,12 +7916,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>59,38%</t>
+          <t>58,59%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>80,31%</t>
+          <t>80,58%</t>
         </is>
       </c>
     </row>
@@ -8061,12 +8061,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>64661</t>
+          <t>65393</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>86294</t>
+          <t>86513</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8076,12 +8076,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>34,74%</t>
+          <t>35,13%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>46,36%</t>
+          <t>46,48%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8096,12 +8096,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>58840</t>
+          <t>59236</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>80979</t>
+          <t>80282</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8111,12 +8111,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>31,8%</t>
+          <t>32,01%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>43,76%</t>
+          <t>43,38%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8131,12 +8131,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>130332</t>
+          <t>130308</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>158646</t>
+          <t>160919</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8151,7 +8151,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>42,74%</t>
+          <t>43,35%</t>
         </is>
       </c>
     </row>
@@ -8174,12 +8174,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>99829</t>
+          <t>99610</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>121462</t>
+          <t>120730</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8189,12 +8189,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>53,64%</t>
+          <t>53,52%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>65,26%</t>
+          <t>64,87%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8209,12 +8209,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>104081</t>
+          <t>104778</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>126220</t>
+          <t>125824</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8224,12 +8224,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>56,24%</t>
+          <t>56,62%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>68,2%</t>
+          <t>67,99%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8244,12 +8244,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>212536</t>
+          <t>210263</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>240850</t>
+          <t>240874</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8259,7 +8259,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>57,26%</t>
+          <t>56,65%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -8638,12 +8638,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5537</t>
+          <t>5744</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12693</t>
+          <t>12390</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8653,12 +8653,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>31,91%</t>
+          <t>33,1%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>73,15%</t>
+          <t>71,41%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8673,12 +8673,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4383</t>
+          <t>4796</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15967</t>
+          <t>15417</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8688,12 +8688,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>53,42%</t>
+          <t>51,58%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8708,12 +8708,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>11275</t>
+          <t>11723</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>25800</t>
+          <t>26008</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8723,12 +8723,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>23,87%</t>
+          <t>24,82%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>54,61%</t>
+          <t>55,05%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>4659</t>
+          <t>4962</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11815</t>
+          <t>11608</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>28,59%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>68,09%</t>
+          <t>66,9%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13922</t>
+          <t>14472</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>25506</t>
+          <t>25093</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>46,58%</t>
+          <t>48,42%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>85,34%</t>
+          <t>83,95%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>21440</t>
+          <t>21232</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>35965</t>
+          <t>35517</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>45,39%</t>
+          <t>44,95%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>76,13%</t>
+          <t>75,18%</t>
         </is>
       </c>
     </row>
@@ -8981,12 +8981,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1019</t>
+          <t>1008</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5815</t>
+          <t>6022</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8996,12 +8996,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,78%</t>
+          <t>32,91%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9016,12 +9016,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>6040</t>
+          <t>5911</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14039</t>
+          <t>14593</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>25,94%</t>
+          <t>25,39%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>60,3%</t>
+          <t>62,68%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8475</t>
+          <t>8028</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>18755</t>
+          <t>18061</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -9066,12 +9066,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>19,31%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>45,11%</t>
+          <t>43,44%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>12483</t>
+          <t>12276</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>17279</t>
+          <t>17290</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>68,22%</t>
+          <t>67,09%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,43%</t>
+          <t>94,49%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>9244</t>
+          <t>8690</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>17243</t>
+          <t>17372</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>39,7%</t>
+          <t>37,32%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>74,06%</t>
+          <t>74,61%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>22826</t>
+          <t>23520</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>33106</t>
+          <t>33553</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>54,89%</t>
+          <t>56,56%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>79,62%</t>
+          <t>80,69%</t>
         </is>
       </c>
     </row>
@@ -9324,12 +9324,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1724</t>
+          <t>1557</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6974</t>
+          <t>6786</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -9339,12 +9339,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>12,36%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>55,36%</t>
+          <t>53,87%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -9359,12 +9359,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4655</t>
+          <t>4538</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11033</t>
+          <t>10905</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9374,12 +9374,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>34,76%</t>
+          <t>33,89%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>82,39%</t>
+          <t>81,43%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9394,12 +9394,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>7295</t>
+          <t>7509</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>16072</t>
+          <t>16486</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9409,12 +9409,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>28,07%</t>
+          <t>28,89%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>61,84%</t>
+          <t>63,44%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5623</t>
+          <t>5811</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10873</t>
+          <t>11040</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>44,64%</t>
+          <t>46,13%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>86,31%</t>
+          <t>87,64%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2358</t>
+          <t>2486</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>8736</t>
+          <t>8853</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>18,57%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>65,24%</t>
+          <t>66,11%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>9916</t>
+          <t>9502</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>18693</t>
+          <t>18479</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>38,16%</t>
+          <t>36,56%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>71,93%</t>
+          <t>71,11%</t>
         </is>
       </c>
     </row>
@@ -9667,12 +9667,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15797</t>
+          <t>16123</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>26969</t>
+          <t>27097</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9682,12 +9682,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>36,17%</t>
+          <t>36,92%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>61,76%</t>
+          <t>62,05%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9702,12 +9702,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17668</t>
+          <t>18242</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>34634</t>
+          <t>34973</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9717,12 +9717,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>29,07%</t>
+          <t>30,01%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>56,99%</t>
+          <t>57,54%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9737,12 +9737,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>37457</t>
+          <t>37013</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>57108</t>
+          <t>57160</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9752,12 +9752,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>35,86%</t>
+          <t>35,44%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>54,68%</t>
+          <t>54,73%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>16700</t>
+          <t>16572</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>27872</t>
+          <t>27546</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>38,24%</t>
+          <t>37,95%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>63,83%</t>
+          <t>63,08%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>26142</t>
+          <t>25803</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>43108</t>
+          <t>42534</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>43,01%</t>
+          <t>42,46%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>70,93%</t>
+          <t>69,99%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>47337</t>
+          <t>47285</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>66988</t>
+          <t>67432</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>45,32%</t>
+          <t>45,27%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>64,14%</t>
+          <t>64,56%</t>
         </is>
       </c>
     </row>
@@ -10010,12 +10010,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5044</t>
+          <t>5009</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12983</t>
+          <t>13809</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>40,55%</t>
+          <t>43,12%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -10045,12 +10045,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>8587</t>
+          <t>8000</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>33247</t>
+          <t>33040</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -10060,12 +10060,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>69,44%</t>
+          <t>69,01%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -10080,12 +10080,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>16856</t>
+          <t>16740</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>49815</t>
+          <t>47648</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -10095,12 +10095,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>20,95%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>62,35%</t>
+          <t>59,63%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>19039</t>
+          <t>18213</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>26978</t>
+          <t>27013</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>59,45%</t>
+          <t>56,88%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>84,25%</t>
+          <t>84,36%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>14630</t>
+          <t>14837</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>39290</t>
+          <t>39877</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>30,56%</t>
+          <t>30,99%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>82,07%</t>
+          <t>83,29%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>30084</t>
+          <t>32251</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>63043</t>
+          <t>63159</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>37,65%</t>
+          <t>40,37%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>78,9%</t>
+          <t>79,05%</t>
         </is>
       </c>
     </row>
@@ -10353,12 +10353,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1082</t>
+          <t>1092</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6418</t>
+          <t>6600</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10368,12 +10368,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>36,82%</t>
+          <t>37,87%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>928</t>
+          <t>915</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7060</t>
+          <t>6843</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>38,49%</t>
+          <t>37,31%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -10423,12 +10423,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3144</t>
+          <t>3051</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>10912</t>
+          <t>11334</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10438,12 +10438,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,79%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>30,5%</t>
+          <t>31,69%</t>
         </is>
       </c>
     </row>
@@ -10466,12 +10466,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>11011</t>
+          <t>10829</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>16347</t>
+          <t>16337</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10481,12 +10481,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>63,18%</t>
+          <t>62,13%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>93,79%</t>
+          <t>93,74%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10501,12 +10501,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>11283</t>
+          <t>11500</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>17415</t>
+          <t>17428</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10516,12 +10516,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>61,51%</t>
+          <t>62,69%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>94,94%</t>
+          <t>95,01%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10536,12 +10536,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>24860</t>
+          <t>24438</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>32628</t>
+          <t>32721</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10551,12 +10551,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>69,5%</t>
+          <t>68,31%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>91,21%</t>
+          <t>91,47%</t>
         </is>
       </c>
     </row>
@@ -10696,12 +10696,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>39882</t>
+          <t>39975</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>59093</t>
+          <t>59450</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10711,12 +10711,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>28,21%</t>
+          <t>28,28%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>41,8%</t>
+          <t>42,05%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>59037</t>
+          <t>58960</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>100342</t>
+          <t>94954</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>30,5%</t>
+          <t>30,46%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>51,84%</t>
+          <t>49,06%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10766,12 +10766,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>105824</t>
+          <t>106381</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>149185</t>
+          <t>148861</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10781,12 +10781,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>31,6%</t>
+          <t>31,76%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>44,54%</t>
+          <t>44,45%</t>
         </is>
       </c>
     </row>
@@ -10809,12 +10809,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>82274</t>
+          <t>81917</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>101485</t>
+          <t>101392</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10824,12 +10824,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>58,2%</t>
+          <t>57,95%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>71,79%</t>
+          <t>71,72%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>93217</t>
+          <t>98605</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>134522</t>
+          <t>134599</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10859,12 +10859,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>48,16%</t>
+          <t>50,94%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>69,5%</t>
+          <t>69,54%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10879,12 +10879,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>185740</t>
+          <t>186064</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>229101</t>
+          <t>228544</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10894,12 +10894,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>55,46%</t>
+          <t>55,55%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>68,4%</t>
+          <t>68,24%</t>
         </is>
       </c>
     </row>
